--- a/salidas/empresas/DHR.xlsx
+++ b/salidas/empresas/DHR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>11.30558109283447</v>
+        <v>11.30558300018311</v>
       </c>
       <c r="C2" t="n">
         <v>19.0344066619873</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>12.09202194213867</v>
+        <v>12.09202289581299</v>
       </c>
       <c r="C3" t="n">
         <v>20.35848045349121</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>12.68883037567139</v>
+        <v>12.68882846832275</v>
       </c>
       <c r="C4" t="n">
         <v>21.3565788269043</v>
@@ -539,7 +551,7 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
@@ -558,7 +570,7 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>12.84664726257324</v>
+        <v>12.84665012359619</v>
       </c>
       <c r="C7" t="n">
         <v>21.61534309387207</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>13.02240467071533</v>
+        <v>13.02240657806396</v>
       </c>
       <c r="C8" t="n">
         <v>21.91107559204102</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>13.24011898040771</v>
+        <v>13.2401180267334</v>
       </c>
       <c r="C9" t="n">
         <v>22.27738189697266</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>13.71953392028809</v>
+        <v>13.71953964233398</v>
       </c>
       <c r="C10" t="n">
         <v>23.07720184326172</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>14.33887672424316</v>
+        <v>14.33888626098633</v>
       </c>
       <c r="C11" t="n">
         <v>24.11898612976074</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>14.60860157012939</v>
+        <v>14.60859489440918</v>
       </c>
       <c r="C12" t="n">
         <v>24.57266616821289</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>14.47671413421631</v>
+        <v>14.47671604156494</v>
       </c>
       <c r="C13" t="n">
         <v>24.34414672851562</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>14.80046653747559</v>
+        <v>14.80046939849854</v>
       </c>
       <c r="C14" t="n">
         <v>24.88856315612793</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>14.32683658599854</v>
+        <v>14.32682991027832</v>
       </c>
       <c r="C15" t="n">
         <v>24.09210205078125</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>14.28285503387451</v>
+        <v>14.28286075592041</v>
       </c>
       <c r="C16" t="n">
         <v>24.01144790649414</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>14.23088836669922</v>
+        <v>14.23088455200195</v>
       </c>
       <c r="C17" t="n">
         <v>23.924072265625</v>
@@ -786,7 +798,7 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>15.09857654571533</v>
+        <v>15.09857368469238</v>
       </c>
       <c r="C19" t="n">
         <v>25.37248802185059</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>14.93458461761475</v>
+        <v>14.93458938598633</v>
       </c>
       <c r="C20" t="n">
         <v>25.09692001342773</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>15.53053188323975</v>
+        <v>15.53053379058838</v>
       </c>
       <c r="C21" t="n">
         <v>26.0983772277832</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>16.54636192321777</v>
+        <v>16.54635047912598</v>
       </c>
       <c r="C22" t="n">
         <v>27.79547691345215</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>17.13851547241211</v>
+        <v>17.13851356506348</v>
       </c>
       <c r="C23" t="n">
         <v>28.79021263122559</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>17.36857604980469</v>
+        <v>17.36857986450195</v>
       </c>
       <c r="C24" t="n">
         <v>29.17668151855469</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>17.55856704711914</v>
+        <v>17.55856895446777</v>
       </c>
       <c r="C25" t="n">
         <v>29.48585510253906</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>15.00102519989014</v>
+        <v>15.00103187561035</v>
       </c>
       <c r="C26" t="n">
         <v>25.19101524353027</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>14.83893013000488</v>
+        <v>14.83893299102783</v>
       </c>
       <c r="C27" t="n">
         <v>24.91880798339844</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>15.22100734710693</v>
+        <v>15.22099781036377</v>
       </c>
       <c r="C28" t="n">
         <v>25.55060005187988</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>15.61940383911133</v>
+        <v>15.61939716339111</v>
       </c>
       <c r="C29" t="n">
         <v>26.21935844421387</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>15.65142917633057</v>
+        <v>15.65142822265625</v>
       </c>
       <c r="C30" t="n">
         <v>26.27312850952148</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>15.48109912872314</v>
+        <v>15.48109436035156</v>
       </c>
       <c r="C31" t="n">
         <v>25.97739410400391</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>15.95173835754395</v>
+        <v>15.95174503326416</v>
       </c>
       <c r="C32" t="n">
         <v>26.76713562011719</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>16.33626365661621</v>
+        <v>16.33625984191895</v>
       </c>
       <c r="C33" t="n">
         <v>27.41236877441406</v>
@@ -1090,7 +1102,7 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>11.86916255950928</v>
+        <v>11.86916351318359</v>
       </c>
       <c r="C35" t="n">
         <v>19.90816116333008</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>11.14787673950195</v>
+        <v>11.1478796005249</v>
       </c>
       <c r="C36" t="n">
         <v>18.6983470916748</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>11.34847259521484</v>
+        <v>11.34847927093506</v>
       </c>
       <c r="C37" t="n">
         <v>19.02432441711426</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>11.21215438842773</v>
+        <v>11.21215724945068</v>
       </c>
       <c r="C38" t="n">
         <v>18.79580497741699</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>10.17574024200439</v>
+        <v>10.17573833465576</v>
       </c>
       <c r="C39" t="n">
         <v>17.05837821960449</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>10.87527751922607</v>
+        <v>10.87527370452881</v>
       </c>
       <c r="C40" t="n">
         <v>18.22114372253418</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>11.72170543670654</v>
+        <v>11.72170925140381</v>
       </c>
       <c r="C41" t="n">
         <v>19.63931465148926</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>12.10480499267578</v>
+        <v>12.10480880737305</v>
       </c>
       <c r="C42" t="n">
         <v>20.28118705749512</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>12.38985919952393</v>
+        <v>12.38985824584961</v>
       </c>
       <c r="C43" t="n">
         <v>20.74831008911133</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>12.28952026367188</v>
+        <v>12.28951358795166</v>
       </c>
       <c r="C44" t="n">
         <v>20.58028030395508</v>
@@ -1305,7 +1317,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
@@ -1330,11 +1342,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>13.5155782699585</v>
+        <v>13.51557540893555</v>
       </c>
       <c r="C46" t="n">
         <v>22.62352180480957</v>
@@ -1355,11 +1367,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>13.69827079772949</v>
+        <v>13.69826602935791</v>
       </c>
       <c r="C47" t="n">
         <v>22.92933654785156</v>
@@ -1380,11 +1392,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>14.2383337020874</v>
+        <v>14.23832988739014</v>
       </c>
       <c r="C48" t="n">
         <v>23.83333587646484</v>
@@ -1405,11 +1417,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>15.1055850982666</v>
+        <v>15.10558223724365</v>
       </c>
       <c r="C49" t="n">
         <v>25.27166938781738</v>
@@ -1430,11 +1442,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>14.33222579956055</v>
+        <v>14.33222389221191</v>
       </c>
       <c r="C50" t="n">
         <v>23.97784233093262</v>
@@ -1455,11 +1467,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>14.85850811004639</v>
+        <v>14.8585090637207</v>
       </c>
       <c r="C51" t="n">
         <v>24.85831642150879</v>
@@ -1480,11 +1492,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>16.05996704101562</v>
+        <v>16.05997085571289</v>
       </c>
       <c r="C52" t="n">
         <v>26.8545093536377</v>
@@ -1505,11 +1517,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>16.93824577331543</v>
+        <v>16.93823623657227</v>
       </c>
       <c r="C53" t="n">
         <v>28.32308959960938</v>
@@ -1530,11 +1542,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>15.95345878601074</v>
+        <v>15.95345211029053</v>
       </c>
       <c r="C54" t="n">
         <v>26.67639923095703</v>
@@ -1555,11 +1567,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>14.92796611785889</v>
+        <v>14.92796897888184</v>
       </c>
       <c r="C55" t="n">
         <v>24.94905281066895</v>
@@ -1580,11 +1592,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>15.44674682617188</v>
+        <v>15.44675064086914</v>
       </c>
       <c r="C56" t="n">
         <v>25.81608772277832</v>
@@ -1605,11 +1617,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>14.61026477813721</v>
+        <v>14.61026668548584</v>
       </c>
       <c r="C57" t="n">
         <v>24.4180793762207</v>
@@ -1630,11 +1642,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>16.33944892883301</v>
+        <v>16.33945083618164</v>
       </c>
       <c r="C58" t="n">
         <v>27.29474830627441</v>
@@ -1655,11 +1667,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>17.44591331481934</v>
+        <v>17.44591903686523</v>
       </c>
       <c r="C59" t="n">
         <v>29.14307594299316</v>
@@ -1680,7 +1692,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
@@ -1705,11 +1717,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>18.98690986633301</v>
+        <v>18.98691749572754</v>
       </c>
       <c r="C61" t="n">
         <v>31.70384788513184</v>
@@ -1730,11 +1742,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>18.54011154174805</v>
+        <v>18.54011344909668</v>
       </c>
       <c r="C62" t="n">
         <v>30.95779609680176</v>
@@ -1755,11 +1767,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>20.3675537109375</v>
+        <v>20.3675651550293</v>
       </c>
       <c r="C63" t="n">
         <v>34.00921630859375</v>
@@ -1784,11 +1796,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>20.89898872375488</v>
+        <v>20.89898681640625</v>
       </c>
       <c r="C64" t="n">
         <v>34.88297271728516</v>
@@ -1813,11 +1825,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>22.24393463134766</v>
+        <v>22.24393081665039</v>
       </c>
       <c r="C65" t="n">
         <v>37.12784957885742</v>
@@ -1842,11 +1854,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>21.95802688598633</v>
+        <v>21.95803260803223</v>
       </c>
       <c r="C66" t="n">
         <v>36.65064239501953</v>
@@ -1871,11 +1883,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>21.3459529876709</v>
+        <v>21.34594345092773</v>
       </c>
       <c r="C67" t="n">
         <v>35.61558151245117</v>
@@ -1900,11 +1912,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>19.7829761505127</v>
+        <v>19.78296661376953</v>
       </c>
       <c r="C68" t="n">
         <v>33.00775909423828</v>
@@ -1929,11 +1941,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>18.45362854003906</v>
+        <v>18.45362663269043</v>
       </c>
       <c r="C69" t="n">
         <v>30.78976631164551</v>
@@ -1958,11 +1970,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>16.90423393249512</v>
+        <v>16.90422439575195</v>
       </c>
       <c r="C70" t="n">
         <v>28.18866539001465</v>
@@ -1987,7 +1999,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
@@ -2016,11 +2028,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>19.49992179870605</v>
+        <v>19.49991798400879</v>
       </c>
       <c r="C72" t="n">
         <v>32.51711273193359</v>
@@ -2045,11 +2057,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>18.96976470947266</v>
+        <v>18.96977615356445</v>
       </c>
       <c r="C73" t="n">
         <v>31.6164722442627</v>
@@ -2074,7 +2086,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
@@ -2103,11 +2115,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>21.3047046661377</v>
+        <v>21.30470085144043</v>
       </c>
       <c r="C75" t="n">
         <v>35.50804138183594</v>
@@ -2132,7 +2144,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
@@ -2161,7 +2173,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
@@ -2190,11 +2202,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>20.96736335754395</v>
+        <v>20.96737480163574</v>
       </c>
       <c r="C78" t="n">
         <v>34.93001937866211</v>
@@ -2219,11 +2231,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>21.02218627929688</v>
+        <v>21.02219390869141</v>
       </c>
       <c r="C79" t="n">
         <v>35.00395202636719</v>
@@ -2248,7 +2260,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
@@ -2277,11 +2289,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>21.62363243103027</v>
+        <v>21.62364387512207</v>
       </c>
       <c r="C81" t="n">
         <v>36.00540924072266</v>
@@ -2306,11 +2318,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>22.2716064453125</v>
+        <v>22.27160453796387</v>
       </c>
       <c r="C82" t="n">
         <v>37.06735610961914</v>
@@ -2335,11 +2347,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>20.8904857635498</v>
+        <v>20.89049339294434</v>
       </c>
       <c r="C83" t="n">
         <v>34.76871109008789</v>
@@ -2364,11 +2376,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>21.79508781433105</v>
+        <v>21.79508018493652</v>
       </c>
       <c r="C84" t="n">
         <v>36.27425765991211</v>
@@ -2393,11 +2405,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>22.58503913879395</v>
+        <v>22.58503341674805</v>
       </c>
       <c r="C85" t="n">
         <v>37.57144546508789</v>
@@ -2422,11 +2434,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>24.2132568359375</v>
+        <v>24.2132511138916</v>
       </c>
       <c r="C86" t="n">
         <v>40.28008651733398</v>
@@ -2451,11 +2463,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>24.88797760009766</v>
+        <v>24.88797187805176</v>
       </c>
       <c r="C87" t="n">
         <v>41.40252304077148</v>
@@ -2480,11 +2492,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>25.12048530578613</v>
+        <v>25.1204776763916</v>
       </c>
       <c r="C88" t="n">
         <v>41.77219009399414</v>
@@ -2509,7 +2521,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
@@ -2538,11 +2550,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>24.98709487915039</v>
+        <v>24.98709297180176</v>
       </c>
       <c r="C90" t="n">
         <v>41.55038833618164</v>
@@ -2567,11 +2579,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>25.5955696105957</v>
+        <v>25.59557151794434</v>
       </c>
       <c r="C91" t="n">
         <v>42.54512786865234</v>
@@ -2596,11 +2608,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>27.22915649414062</v>
+        <v>27.22916412353516</v>
       </c>
       <c r="C92" t="n">
         <v>45.2604866027832</v>
@@ -2625,11 +2637,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>26.49323272705078</v>
+        <v>26.49324035644531</v>
       </c>
       <c r="C93" t="n">
         <v>44.0372314453125</v>
@@ -2654,11 +2666,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>28.03995704650879</v>
+        <v>28.03994941711426</v>
       </c>
       <c r="C94" t="n">
         <v>46.59128189086914</v>
@@ -2683,11 +2695,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>29.16042137145996</v>
+        <v>29.16041946411133</v>
       </c>
       <c r="C95" t="n">
         <v>48.45305252075195</v>
@@ -2712,11 +2724,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>30.25661277770996</v>
+        <v>30.25660705566406</v>
       </c>
       <c r="C96" t="n">
         <v>50.27449417114258</v>
@@ -2741,11 +2753,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>31.23757743835449</v>
+        <v>31.23758697509766</v>
       </c>
       <c r="C97" t="n">
         <v>51.88758087158203</v>
@@ -2770,7 +2782,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
@@ -2799,11 +2811,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>30.95028877258301</v>
+        <v>30.95029258728027</v>
       </c>
       <c r="C99" t="n">
         <v>51.41037368774414</v>
@@ -2828,7 +2840,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
@@ -2857,11 +2869,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>29.73182106018066</v>
+        <v>29.73183441162109</v>
       </c>
       <c r="C101" t="n">
         <v>49.32008361816406</v>
@@ -2886,7 +2898,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
@@ -2915,11 +2927,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>31.9398250579834</v>
+        <v>31.9398193359375</v>
       </c>
       <c r="C103" t="n">
         <v>52.91592025756836</v>
@@ -2944,11 +2956,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>29.97224998474121</v>
+        <v>29.97224044799805</v>
       </c>
       <c r="C104" t="n">
         <v>49.65614318847656</v>
@@ -2973,11 +2985,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>31.07976341247559</v>
+        <v>31.07977485656738</v>
       </c>
       <c r="C105" t="n">
         <v>51.49102783203125</v>
@@ -3002,11 +3014,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>30.86404991149902</v>
+        <v>30.86404228210449</v>
       </c>
       <c r="C106" t="n">
         <v>51.06759262084961</v>
@@ -3031,11 +3043,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>32.65951156616211</v>
+        <v>32.65950393676758</v>
       </c>
       <c r="C107" t="n">
         <v>54.03836059570312</v>
@@ -3060,7 +3072,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
@@ -3089,11 +3101,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>34.85654067993164</v>
+        <v>34.85655212402344</v>
       </c>
       <c r="C109" t="n">
         <v>57.6073112487793</v>
@@ -3118,11 +3130,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>33.50229644775391</v>
+        <v>33.5023078918457</v>
       </c>
       <c r="C110" t="n">
         <v>55.36915588378906</v>
@@ -3147,11 +3159,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>35.49502182006836</v>
+        <v>35.49502944946289</v>
       </c>
       <c r="C111" t="n">
         <v>58.66253662109375</v>
@@ -3176,11 +3188,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>34.58145141601562</v>
+        <v>34.58145904541016</v>
       </c>
       <c r="C112" t="n">
         <v>57.06289291381836</v>
@@ -3205,11 +3217,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>33.35135269165039</v>
+        <v>33.35135650634766</v>
       </c>
       <c r="C113" t="n">
         <v>55.03309631347656</v>
@@ -3234,11 +3246,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>35.15984344482422</v>
+        <v>35.15984725952148</v>
       </c>
       <c r="C114" t="n">
         <v>58.01730346679688</v>
@@ -3263,11 +3275,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>34.91749954223633</v>
+        <v>34.91749572753906</v>
       </c>
       <c r="C115" t="n">
         <v>57.52665710449219</v>
@@ -3292,7 +3304,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
@@ -3321,11 +3333,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>35.50089645385742</v>
+        <v>35.50087738037109</v>
       </c>
       <c r="C117" t="n">
         <v>58.48778533935547</v>
@@ -3350,11 +3362,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>34.81897354125977</v>
+        <v>34.81896209716797</v>
       </c>
       <c r="C118" t="n">
         <v>57.2712516784668</v>
@@ -3379,11 +3391,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>38.12881851196289</v>
+        <v>38.12882232666016</v>
       </c>
       <c r="C119" t="n">
         <v>62.71541213989258</v>
@@ -3408,11 +3420,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>39.38740158081055</v>
+        <v>39.38739395141602</v>
       </c>
       <c r="C120" t="n">
         <v>64.78553771972656</v>
@@ -3437,11 +3449,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>38.00763702392578</v>
+        <v>38.00762176513672</v>
       </c>
       <c r="C121" t="n">
         <v>62.4264030456543</v>
@@ -3466,7 +3478,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
@@ -3495,11 +3507,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>36.53036880493164</v>
+        <v>36.53036499023438</v>
       </c>
       <c r="C123" t="n">
         <v>60.00005340576172</v>
@@ -3524,7 +3536,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
@@ -3553,11 +3565,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>39.65817260742188</v>
+        <v>39.65817642211914</v>
       </c>
       <c r="C125" t="n">
         <v>65.02750396728516</v>
@@ -3582,11 +3594,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>40.31811141967773</v>
+        <v>40.3181266784668</v>
       </c>
       <c r="C126" t="n">
         <v>66.10961151123047</v>
@@ -3611,11 +3623,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>41.46772003173828</v>
+        <v>41.46771621704102</v>
       </c>
       <c r="C127" t="n">
         <v>67.88401031494141</v>
@@ -3640,7 +3652,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
@@ -3669,11 +3681,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>68.57810211181641</v>
+        <v>68.57811737060547</v>
       </c>
       <c r="C129" t="n">
         <v>72.17198944091797</v>
@@ -3698,11 +3710,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>66.140625</v>
+        <v>66.14065551757812</v>
       </c>
       <c r="C130" t="n">
         <v>69.49468231201172</v>
@@ -3727,7 +3739,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
@@ -3756,11 +3768,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>65.95503234863281</v>
+        <v>65.95501708984375</v>
       </c>
       <c r="C132" t="n">
         <v>69.29964447021484</v>
@@ -3785,11 +3797,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>65.78094482421875</v>
+        <v>65.78089904785156</v>
       </c>
       <c r="C133" t="n">
         <v>69.00709533691406</v>
@@ -3814,11 +3826,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>70.91897583007812</v>
+        <v>70.91899108886719</v>
       </c>
       <c r="C134" t="n">
         <v>74.39716339111328</v>
@@ -3843,11 +3855,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>72.29647827148438</v>
+        <v>72.29644012451172</v>
       </c>
       <c r="C135" t="n">
         <v>75.84220123291016</v>
@@ -3872,11 +3884,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>72.39756774902344</v>
+        <v>72.39756011962891</v>
       </c>
       <c r="C136" t="n">
         <v>75.82447052001953</v>
@@ -3901,11 +3913,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>70.53537750244141</v>
+        <v>70.53534698486328</v>
       </c>
       <c r="C137" t="n">
         <v>73.87411499023438</v>
@@ -3930,11 +3942,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>71.89813995361328</v>
+        <v>71.89813232421875</v>
       </c>
       <c r="C138" t="n">
         <v>75.30141448974609</v>
@@ -3959,11 +3971,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>71.55096435546875</v>
+        <v>71.55094909667969</v>
       </c>
       <c r="C139" t="n">
         <v>74.81382751464844</v>
@@ -3988,11 +4000,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>69.09217834472656</v>
+        <v>69.09219360351562</v>
       </c>
       <c r="C140" t="n">
         <v>72.24290466308594</v>
@@ -4017,11 +4029,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>70.72858428955078</v>
+        <v>70.72856140136719</v>
       </c>
       <c r="C141" t="n">
         <v>73.95390319824219</v>
@@ -4046,11 +4058,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>72.84883880615234</v>
+        <v>72.84885406494141</v>
       </c>
       <c r="C142" t="n">
         <v>76.04609680175781</v>
@@ -4075,11 +4087,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>78.36050415039062</v>
+        <v>78.36049652099609</v>
       </c>
       <c r="C143" t="n">
         <v>81.79964447021484</v>
@@ -4104,7 +4116,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
@@ -4133,11 +4145,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>78.94570159912109</v>
+        <v>78.94572448730469</v>
       </c>
       <c r="C145" t="n">
         <v>82.2872314453125</v>
@@ -4162,11 +4174,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>86.14114379882812</v>
+        <v>86.14115905761719</v>
       </c>
       <c r="C146" t="n">
         <v>89.7872314453125</v>
@@ -4191,11 +4203,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>83.16432189941406</v>
+        <v>83.16429901123047</v>
       </c>
       <c r="C147" t="n">
         <v>86.68439483642578</v>
@@ -4220,11 +4232,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>83.41212463378906</v>
+        <v>83.41211700439453</v>
       </c>
       <c r="C148" t="n">
         <v>86.79964447021484</v>
@@ -4249,11 +4261,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>85.46526336669922</v>
+        <v>85.46524810791016</v>
       </c>
       <c r="C149" t="n">
         <v>88.93617248535156</v>
@@ -4278,11 +4290,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>84.57925415039062</v>
+        <v>84.57926177978516</v>
       </c>
       <c r="C150" t="n">
         <v>88.01418304443359</v>
@@ -4307,11 +4319,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>84.20537567138672</v>
+        <v>84.20539855957031</v>
       </c>
       <c r="C151" t="n">
         <v>87.48226928710938</v>
@@ -4336,11 +4348,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>87.53330993652344</v>
+        <v>87.53329467773438</v>
       </c>
       <c r="C152" t="n">
         <v>90.93971252441406</v>
@@ -4365,11 +4377,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>88.35250854492188</v>
+        <v>88.35247802734375</v>
       </c>
       <c r="C153" t="n">
         <v>91.79077911376953</v>
@@ -4394,11 +4406,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>92.85789489746094</v>
+        <v>92.85791778564453</v>
       </c>
       <c r="C154" t="n">
         <v>96.32978820800781</v>
@@ -4423,11 +4435,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>84.94455718994141</v>
+        <v>84.94457244873047</v>
       </c>
       <c r="C155" t="n">
         <v>88.12056732177734</v>
@@ -4452,11 +4464,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>93.60991668701172</v>
+        <v>93.60993957519531</v>
       </c>
       <c r="C156" t="n">
         <v>97.10993194580078</v>
@@ -4481,11 +4493,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>88.26486206054688</v>
+        <v>88.26486968994141</v>
       </c>
       <c r="C157" t="n">
         <v>91.41844177246094</v>
@@ -4510,11 +4522,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>94.94120025634766</v>
+        <v>94.94120788574219</v>
       </c>
       <c r="C158" t="n">
         <v>98.33333587646484</v>
@@ -4539,11 +4551,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>108.7219314575195</v>
+        <v>108.721923828125</v>
       </c>
       <c r="C159" t="n">
         <v>112.6063842773438</v>
@@ -4568,7 +4580,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
@@ -4597,11 +4609,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>113.5098419189453</v>
+        <v>113.5098342895508</v>
       </c>
       <c r="C161" t="n">
         <v>117.4113464355469</v>
@@ -4626,11 +4638,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>113.1413040161133</v>
+        <v>113.1413116455078</v>
       </c>
       <c r="C162" t="n">
         <v>117.030143737793</v>
@@ -4655,11 +4667,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>122.6398391723633</v>
+        <v>122.6398468017578</v>
       </c>
       <c r="C163" t="n">
         <v>126.7021255493164</v>
@@ -4684,11 +4696,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>120.5632705688477</v>
+        <v>120.5632629394531</v>
       </c>
       <c r="C164" t="n">
         <v>124.5567398071289</v>
@@ -4713,11 +4725,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>121.9276275634766</v>
+        <v>121.9276428222656</v>
       </c>
       <c r="C165" t="n">
         <v>125.96630859375</v>
@@ -4742,11 +4754,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>124.0821304321289</v>
+        <v>124.0821228027344</v>
       </c>
       <c r="C166" t="n">
         <v>128.0407867431641</v>
@@ -4771,7 +4783,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
@@ -4800,11 +4812,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>125.4137573242188</v>
+        <v>125.4137344360352</v>
       </c>
       <c r="C168" t="n">
         <v>129.4148864746094</v>
@@ -4829,11 +4841,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>132.0034332275391</v>
+        <v>132.0034637451172</v>
       </c>
       <c r="C169" t="n">
         <v>136.0638275146484</v>
@@ -4858,11 +4870,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>138.359375</v>
+        <v>138.3593902587891</v>
       </c>
       <c r="C170" t="n">
         <v>142.6152496337891</v>
@@ -4887,11 +4899,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>124.3488388061523</v>
+        <v>124.3488464355469</v>
       </c>
       <c r="C171" t="n">
         <v>128.1737518310547</v>
@@ -4916,11 +4928,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>119.2081527709961</v>
+        <v>119.2081298828125</v>
       </c>
       <c r="C172" t="n">
         <v>122.7039031982422</v>
@@ -4945,11 +4957,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>140.7829132080078</v>
+        <v>140.782958984375</v>
       </c>
       <c r="C173" t="n">
         <v>144.9113464355469</v>
@@ -4974,11 +4986,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>143.4959259033203</v>
+        <v>143.4959411621094</v>
       </c>
       <c r="C174" t="n">
         <v>147.7039031982422</v>
@@ -5003,11 +5015,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>152.4581298828125</v>
+        <v>152.4580993652344</v>
       </c>
       <c r="C175" t="n">
         <v>156.7641906738281</v>
@@ -5032,11 +5044,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>175.7109375</v>
+        <v>175.7109527587891</v>
       </c>
       <c r="C176" t="n">
         <v>180.6737518310547</v>
@@ -5061,11 +5073,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>178.0129699707031</v>
+        <v>178.0129089355469</v>
       </c>
       <c r="C177" t="n">
         <v>183.0407867431641</v>
@@ -5090,11 +5102,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>185.8160552978516</v>
+        <v>185.8159942626953</v>
       </c>
       <c r="C178" t="n">
         <v>190.8953857421875</v>
@@ -5119,11 +5131,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>198.0783386230469</v>
+        <v>198.0783081054688</v>
       </c>
       <c r="C179" t="n">
         <v>203.4929046630859</v>
@@ -5148,7 +5160,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -5177,7 +5189,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
@@ -5206,11 +5218,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>205.4083404541016</v>
+        <v>205.4082946777344</v>
       </c>
       <c r="C182" t="n">
         <v>210.8510589599609</v>
@@ -5235,11 +5247,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>189.7160339355469</v>
+        <v>189.7160491943359</v>
       </c>
       <c r="C183" t="n">
         <v>194.7429046630859</v>
@@ -5264,11 +5276,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>194.5744934082031</v>
+        <v>194.574462890625</v>
       </c>
       <c r="C184" t="n">
         <v>199.5390014648438</v>
@@ -5293,11 +5305,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>219.52294921875</v>
+        <v>219.5229797363281</v>
       </c>
       <c r="C185" t="n">
         <v>225.1241149902344</v>
@@ -5322,11 +5334,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>221.4248046875</v>
+        <v>221.4248352050781</v>
       </c>
       <c r="C186" t="n">
         <v>227.074462890625</v>
@@ -5351,11 +5363,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>232.1701507568359</v>
+        <v>232.1701049804688</v>
       </c>
       <c r="C187" t="n">
         <v>237.9078063964844</v>
@@ -5380,7 +5392,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
@@ -5409,11 +5421,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>280.4451599121094</v>
+        <v>280.4450988769531</v>
       </c>
       <c r="C189" t="n">
         <v>287.3758850097656</v>
@@ -5438,11 +5450,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>263.566650390625</v>
+        <v>263.5665283203125</v>
       </c>
       <c r="C190" t="n">
         <v>269.8936157226562</v>
@@ -5467,11 +5479,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>269.9125061035156</v>
+        <v>269.9124755859375</v>
       </c>
       <c r="C191" t="n">
         <v>276.391845703125</v>
@@ -5496,11 +5508,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>278.4573364257812</v>
+        <v>278.4573669433594</v>
       </c>
       <c r="C192" t="n">
         <v>285.141845703125</v>
@@ -5525,7 +5537,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -5554,7 +5566,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -5583,11 +5595,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>237.7227172851562</v>
+        <v>237.7226715087891</v>
       </c>
       <c r="C195" t="n">
         <v>243.2712707519531</v>
@@ -5612,11 +5624,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>254.3354644775391</v>
+        <v>254.3354187011719</v>
       </c>
       <c r="C196" t="n">
         <v>260.0443115234375</v>
@@ -5641,11 +5653,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>217.7454376220703</v>
+        <v>217.7454223632812</v>
       </c>
       <c r="C197" t="n">
         <v>222.6329803466797</v>
@@ -5670,11 +5682,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>228.7484588623047</v>
+        <v>228.7484741210938</v>
       </c>
       <c r="C198" t="n">
         <v>233.8829803466797</v>
@@ -5699,11 +5711,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>220.0414276123047</v>
+        <v>220.0413818359375</v>
       </c>
       <c r="C199" t="n">
         <v>224.7517700195312</v>
@@ -5728,11 +5740,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>252.97998046875</v>
+        <v>252.9799346923828</v>
       </c>
       <c r="C200" t="n">
         <v>258.3953857421875</v>
@@ -5757,11 +5769,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>234.2670135498047</v>
+        <v>234.2670440673828</v>
       </c>
       <c r="C201" t="n">
         <v>239.2819213867188</v>
@@ -5786,11 +5798,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>224.3922424316406</v>
+        <v>224.3922271728516</v>
       </c>
       <c r="C202" t="n">
         <v>228.9804992675781</v>
@@ -5815,11 +5827,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>218.6410369873047</v>
+        <v>218.6410522460938</v>
       </c>
       <c r="C203" t="n">
         <v>223.1117095947266</v>
@@ -5844,11 +5856,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>237.5278625488281</v>
+        <v>237.5278778076172</v>
       </c>
       <c r="C204" t="n">
         <v>242.3847503662109</v>
@@ -5873,7 +5885,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
@@ -5902,11 +5914,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>229.9046173095703</v>
+        <v>229.9046478271484</v>
       </c>
       <c r="C206" t="n">
         <v>234.3794403076172</v>
@@ -5931,11 +5943,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>215.2518310546875</v>
+        <v>215.2518157958984</v>
       </c>
       <c r="C207" t="n">
         <v>219.4414825439453</v>
@@ -5960,7 +5972,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5989,11 +6001,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>206.2417297363281</v>
+        <v>206.2417449951172</v>
       </c>
       <c r="C209" t="n">
         <v>210.0265960693359</v>
@@ -6018,11 +6030,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>199.8954315185547</v>
+        <v>199.8954467773438</v>
       </c>
       <c r="C210" t="n">
         <v>203.5638275146484</v>
@@ -6047,11 +6059,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>209.1722869873047</v>
+        <v>209.1723022460938</v>
       </c>
       <c r="C211" t="n">
         <v>212.7659606933594</v>
@@ -6076,7 +6088,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -6105,11 +6117,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>230.9610900878906</v>
+        <v>230.9610595703125</v>
       </c>
       <c r="C213" t="n">
         <v>234.9290771484375</v>
@@ -6134,7 +6146,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6163,7 +6175,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6192,11 +6204,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>219.8096160888672</v>
+        <v>219.8095855712891</v>
       </c>
       <c r="C216" t="n">
         <v>223.3099975585938</v>
@@ -6221,7 +6233,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6250,11 +6262,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>236.3930358886719</v>
+        <v>236.3930511474609</v>
       </c>
       <c r="C218" t="n">
         <v>239.9100036621094</v>
@@ -6279,11 +6291,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>249.4291076660156</v>
+        <v>249.4290924072266</v>
       </c>
       <c r="C219" t="n">
         <v>253.1399993896484</v>
@@ -6308,7 +6320,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6337,11 +6349,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>243.26904296875</v>
+        <v>243.2690277099609</v>
       </c>
       <c r="C221" t="n">
         <v>246.6199951171875</v>
@@ -6366,7 +6378,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6395,7 +6407,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6424,7 +6436,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6453,11 +6465,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>265.9359130859375</v>
+        <v>265.9360046386719</v>
       </c>
       <c r="C225" t="n">
         <v>269.3099975585938</v>
@@ -6482,11 +6494,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>274.8047180175781</v>
+        <v>274.8047485351562</v>
       </c>
       <c r="C226" t="n">
         <v>278.0199890136719</v>
@@ -6511,7 +6523,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6540,11 +6552,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>236.9180297851562</v>
+        <v>236.9180450439453</v>
       </c>
       <c r="C228" t="n">
         <v>239.6900024414062</v>
@@ -6569,7 +6581,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6598,11 +6610,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>220.4213409423828</v>
+        <v>220.4214019775391</v>
       </c>
       <c r="C230" t="n">
         <v>222.7400054931641</v>
@@ -6627,7 +6639,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6656,7 +6668,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6685,11 +6697,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>197.5559387207031</v>
+        <v>197.5559539794922</v>
       </c>
       <c r="C233" t="n">
         <v>199.3300018310547</v>
@@ -6714,11 +6726,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>188.2098693847656</v>
+        <v>188.2098541259766</v>
       </c>
       <c r="C234" t="n">
         <v>189.8999938964844</v>
@@ -6743,11 +6755,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>196.0933532714844</v>
+        <v>196.0933380126953</v>
       </c>
       <c r="C235" t="n">
         <v>197.5399932861328</v>
@@ -6772,11 +6784,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>195.7161407470703</v>
+        <v>195.7161254882812</v>
       </c>
       <c r="C236" t="n">
         <v>197.1600036621094</v>
@@ -6801,7 +6813,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6830,11 +6842,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>197.1557312011719</v>
+        <v>197.1557464599609</v>
       </c>
       <c r="C238" t="n">
         <v>198.2599945068359</v>
@@ -6859,11 +6871,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>214.1804046630859</v>
+        <v>214.180419921875</v>
       </c>
       <c r="C239" t="n">
         <v>215.3800048828125</v>
@@ -6888,7 +6900,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6917,7 +6929,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6946,7 +6958,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6975,7 +6987,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -7004,7 +7016,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7033,7 +7045,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7062,7 +7074,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7091,7 +7103,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7120,7 +7132,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7149,7 +7161,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7178,32 +7190,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>221.5599975585938</v>
+        <v>223.7700042724609</v>
       </c>
       <c r="C250" t="n">
-        <v>221.5599975585938</v>
+        <v>223.7700042724609</v>
       </c>
       <c r="D250" t="n">
-        <v>62829200</v>
+        <v>69025600</v>
       </c>
       <c r="E250" t="n">
         <v>5.640000000000001</v>
       </c>
       <c r="F250" t="n">
-        <v>39.28368751038896</v>
+        <v>39.67553267242215</v>
       </c>
       <c r="G250" t="n">
         <v>702986054</v>
       </c>
       <c r="H250" t="n">
-        <v>155753588407.9655</v>
+        <v>157307192307.0605</v>
       </c>
       <c r="I250" t="n">
-        <v>0.08937474597469042</v>
+        <v>0.09818914558438736</v>
       </c>
     </row>
   </sheetData>
@@ -7235,75 +7247,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39536</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39626</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40017</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7339,13 +7351,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39627</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39717</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40108</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7381,13 +7393,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39906</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40290</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7423,13 +7435,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39907</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39997</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40017</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7465,13 +7477,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39998</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40088</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40108</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7507,13 +7519,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40089</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7540,7 +7552,7 @@
       <c r="I7" t="n">
         <v>1.162765688599251</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="K7" t="n">
@@ -7553,13 +7565,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40270</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40290</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7586,7 +7598,7 @@
       <c r="I8" t="n">
         <v>1.219895794686497</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="K8" t="n">
@@ -7599,13 +7611,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40271</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40361</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40401</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7632,7 +7644,7 @@
       <c r="I9" t="n">
         <v>1.290468278676625</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="K9" t="n">
@@ -7645,13 +7657,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40362</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40472</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7678,7 +7690,7 @@
       <c r="I10" t="n">
         <v>1.576118809112857</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="K10" t="n">
@@ -7691,13 +7703,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40453</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7724,7 +7736,7 @@
       <c r="I11" t="n">
         <v>1.771033288704639</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="K11" t="n">
@@ -7737,13 +7749,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40654</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7770,7 +7782,7 @@
       <c r="I12" t="n">
         <v>1.895375284306293</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40654</v>
       </c>
       <c r="K12" t="n">
@@ -7783,13 +7795,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40635</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40751</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7816,7 +7828,7 @@
       <c r="I13" t="n">
         <v>2.157501653412482</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40751</v>
       </c>
       <c r="K13" t="n">
@@ -7829,13 +7841,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40726</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40836</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7862,7 +7874,7 @@
       <c r="I14" t="n">
         <v>2.016356685432227</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40836</v>
       </c>
       <c r="K14" t="n">
@@ -7875,13 +7887,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7908,7 +7920,7 @@
       <c r="I15" t="n">
         <v>2.090289763898075</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="K15" t="n">
@@ -7921,13 +7933,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40998</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41018</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7954,7 +7966,7 @@
       <c r="I16" t="n">
         <v>2.244877109781212</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41018</v>
       </c>
       <c r="K16" t="n">
@@ -7967,13 +7979,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41109</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -8000,7 +8012,7 @@
       <c r="I17" t="n">
         <v>2.177665220266805</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41109</v>
       </c>
       <c r="K17" t="n">
@@ -8013,13 +8025,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41180</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41200</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8046,7 +8058,7 @@
       <c r="I18" t="n">
         <v>2.197828787121127</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41200</v>
       </c>
       <c r="K18" t="n">
@@ -8059,13 +8071,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41181</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8092,7 +8104,7 @@
       <c r="I19" t="n">
         <v>2.258319487684094</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="K19" t="n">
@@ -8105,13 +8117,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41362</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41382</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8138,7 +8150,7 @@
       <c r="I20" t="n">
         <v>2.338973755101383</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41382</v>
       </c>
       <c r="K20" t="n">
@@ -8151,13 +8163,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41363</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41453</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41473</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8184,7 +8196,7 @@
       <c r="I21" t="n">
         <v>2.359137321955705</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41473</v>
       </c>
       <c r="K21" t="n">
@@ -8197,13 +8209,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41454</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41544</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41564</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8230,7 +8242,7 @@
       <c r="I22" t="n">
         <v>2.40618564461579</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41564</v>
       </c>
       <c r="K22" t="n">
@@ -8243,13 +8255,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41545</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41691</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8276,7 +8288,7 @@
       <c r="I23" t="n">
         <v>2.554051801547487</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41691</v>
       </c>
       <c r="K23" t="n">
@@ -8289,13 +8301,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41726</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41745</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8322,7 +8334,7 @@
       <c r="I24" t="n">
         <v>2.439791589372994</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41745</v>
       </c>
       <c r="K24" t="n">
@@ -8335,13 +8347,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41727</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41817</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41837</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8368,7 +8380,7 @@
       <c r="I25" t="n">
         <v>2.49356110098452</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41837</v>
       </c>
       <c r="K25" t="n">
@@ -8381,13 +8393,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41818</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41908</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41928</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8414,7 +8426,7 @@
       <c r="I26" t="n">
         <v>2.567494179450368</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41928</v>
       </c>
       <c r="K26" t="n">
@@ -8427,13 +8439,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41909</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42060</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8460,7 +8472,7 @@
       <c r="I27" t="n">
         <v>2.439791589372994</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42060</v>
       </c>
       <c r="K27" t="n">
@@ -8473,13 +8485,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42097</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42117</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8506,7 +8518,7 @@
       <c r="I28" t="n">
         <v>2.426349211470113</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42117</v>
       </c>
       <c r="K28" t="n">
@@ -8519,13 +8531,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42098</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42188</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42208</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8552,7 +8564,7 @@
       <c r="I29" t="n">
         <v>2.439791589372994</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42208</v>
       </c>
       <c r="K29" t="n">
@@ -8565,13 +8577,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42189</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42279</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42299</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8598,7 +8610,7 @@
       <c r="I30" t="n">
         <v>3.152237618225714</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42299</v>
       </c>
       <c r="K30" t="n">
@@ -8611,13 +8623,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42280</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42424</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8644,7 +8656,7 @@
       <c r="I31" t="n">
         <v>3.199285940885799</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42424</v>
       </c>
       <c r="K31" t="n">
@@ -8657,13 +8669,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42481</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8690,7 +8702,7 @@
       <c r="I32" t="n">
         <v>3.400921609429022</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42481</v>
       </c>
       <c r="K32" t="n">
@@ -8703,13 +8715,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42462</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42576</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8736,7 +8748,7 @@
       <c r="I33" t="n">
         <v>3.582299614472602</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42576</v>
       </c>
       <c r="K33" t="n">
@@ -8749,13 +8761,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42553</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42663</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8782,7 +8794,7 @@
       <c r="I34" t="n">
         <v>2.72779453594223</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42663</v>
       </c>
       <c r="K34" t="n">
@@ -8795,13 +8807,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42788</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8828,7 +8840,7 @@
       <c r="I35" t="n">
         <v>3.010978390033284</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42788</v>
       </c>
       <c r="K35" t="n">
@@ -8841,13 +8853,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42845</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8874,7 +8886,7 @@
       <c r="I36" t="n">
         <v>2.916666666666667</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42845</v>
       </c>
       <c r="K36" t="n">
@@ -8887,13 +8899,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42936</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8920,7 +8932,7 @@
       <c r="I37" t="n">
         <v>2.783687943262412</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42936</v>
       </c>
       <c r="K37" t="n">
@@ -8933,13 +8945,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43007</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43027</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8966,7 +8978,7 @@
       <c r="I38" t="n">
         <v>3.005319148936171</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43027</v>
       </c>
       <c r="K38" t="n">
@@ -8979,13 +8991,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43152</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9012,7 +9024,7 @@
       <c r="I39" t="n">
         <v>3.129432624113475</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43152</v>
       </c>
       <c r="K39" t="n">
@@ -9025,13 +9037,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43189</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43209</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9058,7 +9070,7 @@
       <c r="I40" t="n">
         <v>3.200354609929079</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43209</v>
       </c>
       <c r="K40" t="n">
@@ -9071,13 +9083,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43280</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43300</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9104,7 +9116,7 @@
       <c r="I41" t="n">
         <v>3.342198581560284</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43300</v>
       </c>
       <c r="K41" t="n">
@@ -9117,13 +9129,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43371</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43391</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9150,7 +9162,7 @@
       <c r="I42" t="n">
         <v>3.448581560283688</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43391</v>
       </c>
       <c r="K42" t="n">
@@ -9163,13 +9175,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43372</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9196,7 +9208,7 @@
       <c r="I43" t="n">
         <v>3.306737588652482</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="K43" t="n">
@@ -9209,13 +9221,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43553</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43573</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9242,7 +9254,7 @@
       <c r="I44" t="n">
         <v>3.005319148936171</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43573</v>
       </c>
       <c r="K44" t="n">
@@ -9255,13 +9267,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43554</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43644</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43664</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9288,7 +9300,7 @@
       <c r="I45" t="n">
         <v>3.023049645390071</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43664</v>
       </c>
       <c r="K45" t="n">
@@ -9301,13 +9313,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43645</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43735</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43762</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9334,7 +9346,7 @@
       <c r="I46" t="n">
         <v>2.98758865248227</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43762</v>
       </c>
       <c r="K46" t="n">
@@ -9347,13 +9359,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43736</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43882</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9380,7 +9392,7 @@
       <c r="I47" t="n">
         <v>3.590425531914894</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43882</v>
       </c>
       <c r="K47" t="n">
@@ -9393,13 +9405,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43924</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9426,7 +9438,7 @@
       <c r="I48" t="n">
         <v>3.900709219858157</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="K48" t="n">
@@ -9439,13 +9451,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43925</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44015</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44035</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9472,7 +9484,7 @@
       <c r="I49" t="n">
         <v>4.140070921985816</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44035</v>
       </c>
       <c r="K49" t="n">
@@ -9485,13 +9497,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44016</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44106</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44126</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9518,7 +9530,7 @@
       <c r="I50" t="n">
         <v>4.379432624113475</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44126</v>
       </c>
       <c r="K50" t="n">
@@ -9531,13 +9543,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44107</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9564,7 +9576,7 @@
       <c r="I51" t="n">
         <v>4.335106382978724</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="K51" t="n">
@@ -9577,13 +9589,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44288</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44308</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9610,7 +9622,7 @@
       <c r="I52" t="n">
         <v>5.647163120567376</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44308</v>
       </c>
       <c r="K52" t="n">
@@ -9623,13 +9635,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44289</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44379</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44399</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9656,7 +9668,7 @@
       <c r="I53" t="n">
         <v>6.675531914893617</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44399</v>
       </c>
       <c r="K53" t="n">
@@ -9669,13 +9681,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44380</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44490</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9702,7 +9714,7 @@
       <c r="I54" t="n">
         <v>7.01241134751773</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44490</v>
       </c>
       <c r="K54" t="n">
@@ -9715,13 +9727,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44471</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44615</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9748,7 +9760,7 @@
       <c r="I55" t="n">
         <v>7.632978723404255</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44615</v>
       </c>
       <c r="K55" t="n">
@@ -9761,13 +9773,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44672</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9794,7 +9806,7 @@
       <c r="I56" t="n">
         <v>7.650709219858157</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44672</v>
       </c>
       <c r="K56" t="n">
@@ -9807,13 +9819,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44653</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44763</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9840,7 +9852,7 @@
       <c r="I57" t="n">
         <v>7.517730496453901</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44763</v>
       </c>
       <c r="K57" t="n">
@@ -9853,13 +9865,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44744</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44854</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9886,7 +9898,7 @@
       <c r="I58" t="n">
         <v>8.014184397163122</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44854</v>
       </c>
       <c r="K58" t="n">
@@ -9899,13 +9911,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44979</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9932,7 +9944,7 @@
       <c r="I59" t="n">
         <v>8.563829787234043</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44979</v>
       </c>
       <c r="K59" t="n">
@@ -9945,13 +9957,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45041</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9978,7 +9990,7 @@
       <c r="I60" t="n">
         <v>8.23581560283688</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45041</v>
       </c>
       <c r="K60" t="n">
@@ -9991,13 +10003,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45132</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10024,7 +10036,7 @@
       <c r="I61" t="n">
         <v>7.562056737588653</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45132</v>
       </c>
       <c r="K61" t="n">
@@ -10037,13 +10049,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45198</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45223</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10070,7 +10082,7 @@
       <c r="I62" t="n">
         <v>7.210354609929079</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45223</v>
       </c>
       <c r="K62" t="n">
@@ -10083,13 +10095,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45343</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10116,7 +10128,7 @@
       <c r="I63" t="n">
         <v>6.000780141843972</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45343</v>
       </c>
       <c r="K63" t="n">
@@ -10129,13 +10141,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45380</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45405</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10162,7 +10174,7 @@
       <c r="I64" t="n">
         <v>5.730921985815603</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45405</v>
       </c>
       <c r="K64" t="n">
@@ -10175,13 +10187,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45381</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45471</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45496</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10208,7 +10220,7 @@
       <c r="I65" t="n">
         <v>5.63</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45496</v>
       </c>
       <c r="K65" t="n">
@@ -10221,13 +10233,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45472</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45562</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45587</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10254,7 +10266,7 @@
       <c r="I66" t="n">
         <v>5.24</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45587</v>
       </c>
       <c r="K66" t="n">
@@ -10267,13 +10279,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45563</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45708</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10300,7 +10312,7 @@
       <c r="I67" t="n">
         <v>5.29</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45708</v>
       </c>
       <c r="K67" t="n">
@@ -10313,13 +10325,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45744</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45769</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10346,7 +10358,7 @@
       <c r="I68" t="n">
         <v>5.16</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45769</v>
       </c>
       <c r="K68" t="n">
@@ -10359,13 +10371,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45745</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45835</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45860</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10392,7 +10404,7 @@
       <c r="I69" t="n">
         <v>4.71</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45860</v>
       </c>
       <c r="K69" t="n">
@@ -10405,13 +10417,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45836</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45926</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45951</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10438,7 +10450,7 @@
       <c r="I70" t="n">
         <v>4.86</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45951</v>
       </c>
       <c r="K70" t="n">
@@ -10451,13 +10463,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45927</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46077</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10484,7 +10496,7 @@
       <c r="I71" t="n">
         <v>5.05</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46077</v>
       </c>
       <c r="K71" t="n">
@@ -10497,13 +10509,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46108</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10530,7 +10542,7 @@
       <c r="I72" t="n">
         <v>5.18</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="K72" t="n">
@@ -10543,13 +10555,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46109</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46199</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46224</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10576,7 +10588,7 @@
       <c r="I73" t="n">
         <v>5.640000000000001</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46224</v>
       </c>
       <c r="K73" t="n">
@@ -10613,52 +10625,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39997</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40017</v>
       </c>
       <c r="C2" t="n">
@@ -10687,10 +10699,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40102</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40108</v>
       </c>
       <c r="C3" t="n">
@@ -10719,10 +10731,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40221</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40233</v>
       </c>
       <c r="C4" t="n">
@@ -10751,10 +10763,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40270</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40290</v>
       </c>
       <c r="C5" t="n">
@@ -10783,10 +10795,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40375</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40401</v>
       </c>
       <c r="C6" t="n">
@@ -10815,10 +10827,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40466</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40472</v>
       </c>
       <c r="C7" t="n">
@@ -10847,10 +10859,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40220</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="C8" t="n">
@@ -10879,10 +10891,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40648</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40654</v>
       </c>
       <c r="C9" t="n">
@@ -10911,10 +10923,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40739</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40751</v>
       </c>
       <c r="C10" t="n">
@@ -10943,10 +10955,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40830</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40836</v>
       </c>
       <c r="C11" t="n">
@@ -10975,10 +10987,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40952</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="C12" t="n">
@@ -11007,10 +11019,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41012</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41018</v>
       </c>
       <c r="C13" t="n">
@@ -11039,10 +11051,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41103</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41109</v>
       </c>
       <c r="C14" t="n">
@@ -11071,10 +11083,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41194</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41200</v>
       </c>
       <c r="C15" t="n">
@@ -11103,10 +11115,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41316</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="C16" t="n">
@@ -11135,10 +11147,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41376</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41382</v>
       </c>
       <c r="C17" t="n">
@@ -11167,10 +11179,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41467</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41473</v>
       </c>
       <c r="C18" t="n">
@@ -11199,10 +11211,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41558</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41564</v>
       </c>
       <c r="C19" t="n">
@@ -11231,10 +11243,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41680</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41691</v>
       </c>
       <c r="C20" t="n">
@@ -11263,10 +11275,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41740</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41745</v>
       </c>
       <c r="C21" t="n">
@@ -11295,10 +11307,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41831</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41837</v>
       </c>
       <c r="C22" t="n">
@@ -11327,10 +11339,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41922</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41928</v>
       </c>
       <c r="C23" t="n">
@@ -11359,10 +11371,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42044</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42060</v>
       </c>
       <c r="C24" t="n">
@@ -11391,10 +11403,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42111</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42117</v>
       </c>
       <c r="C25" t="n">
@@ -11423,10 +11435,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42205</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42208</v>
       </c>
       <c r="C26" t="n">
@@ -11455,10 +11467,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42293</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42299</v>
       </c>
       <c r="C27" t="n">
@@ -11487,10 +11499,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42409</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42424</v>
       </c>
       <c r="C28" t="n">
@@ -11519,10 +11531,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42475</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42481</v>
       </c>
       <c r="C29" t="n">
@@ -11551,10 +11563,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42566</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42576</v>
       </c>
       <c r="C30" t="n">
@@ -11583,10 +11595,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42657</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42663</v>
       </c>
       <c r="C31" t="n">
@@ -11615,10 +11627,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42775</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42788</v>
       </c>
       <c r="C32" t="n">
@@ -11647,10 +11659,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42839</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42845</v>
       </c>
       <c r="C33" t="n">
@@ -11679,10 +11691,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42930</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42936</v>
       </c>
       <c r="C34" t="n">
@@ -11711,10 +11723,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43021</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43027</v>
       </c>
       <c r="C35" t="n">
@@ -11743,10 +11755,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43139</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43152</v>
       </c>
       <c r="C36" t="n">
@@ -11775,10 +11787,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43203</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43209</v>
       </c>
       <c r="C37" t="n">
@@ -11807,10 +11819,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43294</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43300</v>
       </c>
       <c r="C38" t="n">
@@ -11839,10 +11851,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43385</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43391</v>
       </c>
       <c r="C39" t="n">
@@ -11871,10 +11883,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43503</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="C40" t="n">
@@ -11903,10 +11915,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43567</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43573</v>
       </c>
       <c r="C41" t="n">
@@ -11935,10 +11947,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43658</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43664</v>
       </c>
       <c r="C42" t="n">
@@ -11967,10 +11979,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43756</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43762</v>
       </c>
       <c r="C43" t="n">
@@ -11999,10 +12011,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43867</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43882</v>
       </c>
       <c r="C44" t="n">
@@ -12031,10 +12043,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43952</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="C45" t="n">
@@ -12063,10 +12075,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44029</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44035</v>
       </c>
       <c r="C46" t="n">
@@ -12095,10 +12107,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44120</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44126</v>
       </c>
       <c r="C47" t="n">
@@ -12127,10 +12139,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44232</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="C48" t="n">
@@ -12159,10 +12171,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44302</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44308</v>
       </c>
       <c r="C49" t="n">
@@ -12191,10 +12203,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44393</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44399</v>
       </c>
       <c r="C50" t="n">
@@ -12223,10 +12235,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44484</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44490</v>
       </c>
       <c r="C51" t="n">
@@ -12255,10 +12267,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44596</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44615</v>
       </c>
       <c r="C52" t="n">
@@ -12287,10 +12299,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44670</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44672</v>
       </c>
       <c r="C53" t="n">
@@ -12319,10 +12331,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44757</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44763</v>
       </c>
       <c r="C54" t="n">
@@ -12351,10 +12363,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44848</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44854</v>
       </c>
       <c r="C55" t="n">
@@ -12383,10 +12395,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44960</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44979</v>
       </c>
       <c r="C56" t="n">
@@ -12415,10 +12427,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45036</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45041</v>
       </c>
       <c r="C57" t="n">
@@ -12447,10 +12459,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45127</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45132</v>
       </c>
       <c r="C58" t="n">
@@ -12479,10 +12491,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45218</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45223</v>
       </c>
       <c r="C59" t="n">
@@ -12511,10 +12523,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45324</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45343</v>
       </c>
       <c r="C60" t="n">
@@ -12543,10 +12555,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45400</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45405</v>
       </c>
       <c r="C61" t="n">
@@ -12575,10 +12587,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45491</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45496</v>
       </c>
       <c r="C62" t="n">
@@ -12607,10 +12619,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45582</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45587</v>
       </c>
       <c r="C63" t="n">
@@ -12639,10 +12651,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45691</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45708</v>
       </c>
       <c r="C64" t="n">
@@ -12671,10 +12683,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45763</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45769</v>
       </c>
       <c r="C65" t="n">
@@ -12703,10 +12715,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45855</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45860</v>
       </c>
       <c r="C66" t="n">
@@ -12735,10 +12747,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45946</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45951</v>
       </c>
       <c r="C67" t="n">
@@ -12767,10 +12779,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46055</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46077</v>
       </c>
       <c r="C68" t="n">
@@ -12799,10 +12811,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46128</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="C69" t="n">
@@ -12831,10 +12843,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46219</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46224</v>
       </c>
       <c r="C70" t="n">
@@ -12881,12 +12893,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/DHR.xlsx
+++ b/salidas/empresas/DHR.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>11.30558300018311</v>
+        <v>11.30558013916016</v>
       </c>
       <c r="C2" t="n">
         <v>19.0344066619873</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>12.09202289581299</v>
+        <v>12.09201908111572</v>
       </c>
       <c r="C3" t="n">
         <v>20.35848045349121</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>12.80063915252686</v>
+        <v>12.80064487457275</v>
       </c>
       <c r="C5" t="n">
         <v>21.54477119445801</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>12.80063915252686</v>
+        <v>12.80064487457275</v>
       </c>
       <c r="C6" t="n">
         <v>21.54477119445801</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>12.84665012359619</v>
+        <v>12.84664821624756</v>
       </c>
       <c r="C7" t="n">
         <v>21.61534309387207</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>13.02240657806396</v>
+        <v>13.02240943908691</v>
       </c>
       <c r="C8" t="n">
         <v>21.91107559204102</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>13.2401180267334</v>
+        <v>13.24011325836182</v>
       </c>
       <c r="C9" t="n">
         <v>22.27738189697266</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>13.71953964233398</v>
+        <v>13.71953392028809</v>
       </c>
       <c r="C10" t="n">
         <v>23.07720184326172</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>14.33888626098633</v>
+        <v>14.33887577056885</v>
       </c>
       <c r="C11" t="n">
         <v>24.11898612976074</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>14.60859489440918</v>
+        <v>14.60859680175781</v>
       </c>
       <c r="C12" t="n">
         <v>24.57266616821289</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>14.47671604156494</v>
+        <v>14.47671890258789</v>
       </c>
       <c r="C13" t="n">
         <v>24.34414672851562</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>14.80046939849854</v>
+        <v>14.80046463012695</v>
       </c>
       <c r="C14" t="n">
         <v>24.88856315612793</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>14.32682991027832</v>
+        <v>14.3268346786499</v>
       </c>
       <c r="C15" t="n">
         <v>24.09210205078125</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>14.28286075592041</v>
+        <v>14.28285598754883</v>
       </c>
       <c r="C16" t="n">
         <v>24.01144790649414</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>14.69265460968018</v>
+        <v>14.69265365600586</v>
       </c>
       <c r="C18" t="n">
         <v>24.70036888122559</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>15.09857368469238</v>
+        <v>15.0985746383667</v>
       </c>
       <c r="C19" t="n">
         <v>25.37248802185059</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>14.93458938598633</v>
+        <v>14.93458557128906</v>
       </c>
       <c r="C20" t="n">
         <v>25.09692001342773</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>15.53053379058838</v>
+        <v>15.53053092956543</v>
       </c>
       <c r="C21" t="n">
         <v>26.0983772277832</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>16.54635047912598</v>
+        <v>16.54636192321777</v>
       </c>
       <c r="C22" t="n">
         <v>27.79547691345215</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>17.36857986450195</v>
+        <v>17.36857414245605</v>
       </c>
       <c r="C24" t="n">
         <v>29.17668151855469</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>15.00103187561035</v>
+        <v>15.00102996826172</v>
       </c>
       <c r="C26" t="n">
         <v>25.19101524353027</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>14.83893299102783</v>
+        <v>14.83893871307373</v>
       </c>
       <c r="C27" t="n">
         <v>24.91880798339844</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>15.22099781036377</v>
+        <v>15.22100734710693</v>
       </c>
       <c r="C28" t="n">
         <v>25.55060005187988</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>15.61939716339111</v>
+        <v>15.61940097808838</v>
       </c>
       <c r="C29" t="n">
         <v>26.21935844421387</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>15.65142822265625</v>
+        <v>15.65143013000488</v>
       </c>
       <c r="C30" t="n">
         <v>26.27312850952148</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>15.48109436035156</v>
+        <v>15.48109722137451</v>
       </c>
       <c r="C31" t="n">
         <v>25.97739410400391</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>16.33625984191895</v>
+        <v>16.33626556396484</v>
       </c>
       <c r="C33" t="n">
         <v>27.41236877441406</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>13.90479373931885</v>
+        <v>13.90479469299316</v>
       </c>
       <c r="C34" t="n">
         <v>23.3225269317627</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>11.86916351318359</v>
+        <v>11.86916065216064</v>
       </c>
       <c r="C35" t="n">
         <v>19.90816116333008</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>11.1478796005249</v>
+        <v>11.14787769317627</v>
       </c>
       <c r="C36" t="n">
         <v>18.6983470916748</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>11.34847927093506</v>
+        <v>11.34847545623779</v>
       </c>
       <c r="C37" t="n">
         <v>19.02432441711426</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>11.21215724945068</v>
+        <v>11.21215915679932</v>
       </c>
       <c r="C38" t="n">
         <v>18.79580497741699</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>10.17573833465576</v>
+        <v>10.17574501037598</v>
       </c>
       <c r="C39" t="n">
         <v>17.05837821960449</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>10.87527370452881</v>
+        <v>10.87527561187744</v>
       </c>
       <c r="C40" t="n">
         <v>18.22114372253418</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>11.72170925140381</v>
+        <v>11.72170639038086</v>
       </c>
       <c r="C41" t="n">
         <v>19.63931465148926</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>12.28951358795166</v>
+        <v>12.28951835632324</v>
       </c>
       <c r="C44" t="n">
         <v>20.58028030395508</v>
@@ -1321,7 +1321,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>12.18315887451172</v>
+        <v>12.1831579208374</v>
       </c>
       <c r="C45" t="n">
         <v>20.40216827392578</v>
@@ -1346,7 +1346,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>13.51557540893555</v>
+        <v>13.51557159423828</v>
       </c>
       <c r="C46" t="n">
         <v>22.62352180480957</v>
@@ -1371,7 +1371,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>13.69826602935791</v>
+        <v>13.69827461242676</v>
       </c>
       <c r="C47" t="n">
         <v>22.92933654785156</v>
@@ -1396,7 +1396,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>14.23832988739014</v>
+        <v>14.23833847045898</v>
       </c>
       <c r="C48" t="n">
         <v>23.83333587646484</v>
@@ -1421,7 +1421,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>15.10558223724365</v>
+        <v>15.10558032989502</v>
       </c>
       <c r="C49" t="n">
         <v>25.27166938781738</v>
@@ -1446,7 +1446,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>14.33222389221191</v>
+        <v>14.33222484588623</v>
       </c>
       <c r="C50" t="n">
         <v>23.97784233093262</v>
@@ -1471,7 +1471,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>14.8585090637207</v>
+        <v>14.85850811004639</v>
       </c>
       <c r="C51" t="n">
         <v>24.85831642150879</v>
@@ -1496,7 +1496,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>16.05997085571289</v>
+        <v>16.05997467041016</v>
       </c>
       <c r="C52" t="n">
         <v>26.8545093536377</v>
@@ -1521,7 +1521,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>16.93823623657227</v>
+        <v>16.93824195861816</v>
       </c>
       <c r="C53" t="n">
         <v>28.32308959960938</v>
@@ -1546,7 +1546,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>15.95345211029053</v>
+        <v>15.95344829559326</v>
       </c>
       <c r="C54" t="n">
         <v>26.67639923095703</v>
@@ -1571,7 +1571,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>14.92796897888184</v>
+        <v>14.92796421051025</v>
       </c>
       <c r="C55" t="n">
         <v>24.94905281066895</v>
@@ -1596,7 +1596,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>15.44675064086914</v>
+        <v>15.44674873352051</v>
       </c>
       <c r="C56" t="n">
         <v>25.81608772277832</v>
@@ -1621,7 +1621,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>14.61026668548584</v>
+        <v>14.61026477813721</v>
       </c>
       <c r="C57" t="n">
         <v>24.4180793762207</v>
@@ -1646,7 +1646,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>16.33945083618164</v>
+        <v>16.33945655822754</v>
       </c>
       <c r="C58" t="n">
         <v>27.29474830627441</v>
@@ -1671,7 +1671,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>17.44591903686523</v>
+        <v>17.44591331481934</v>
       </c>
       <c r="C59" t="n">
         <v>29.14307594299316</v>
@@ -1721,7 +1721,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>18.98691749572754</v>
+        <v>18.98690986633301</v>
       </c>
       <c r="C61" t="n">
         <v>31.70384788513184</v>
@@ -1746,7 +1746,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>18.54011344909668</v>
+        <v>18.54010772705078</v>
       </c>
       <c r="C62" t="n">
         <v>30.95779609680176</v>
@@ -1771,7 +1771,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>20.3675651550293</v>
+        <v>20.36756134033203</v>
       </c>
       <c r="C63" t="n">
         <v>34.00921630859375</v>
@@ -1800,7 +1800,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>20.89898681640625</v>
+        <v>20.89898490905762</v>
       </c>
       <c r="C64" t="n">
         <v>34.88297271728516</v>
@@ -1829,7 +1829,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>22.24393081665039</v>
+        <v>22.24393653869629</v>
       </c>
       <c r="C65" t="n">
         <v>37.12784957885742</v>
@@ -1858,7 +1858,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>21.95803260803223</v>
+        <v>21.9580249786377</v>
       </c>
       <c r="C66" t="n">
         <v>36.65064239501953</v>
@@ -1887,7 +1887,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>21.34594345092773</v>
+        <v>21.34594917297363</v>
       </c>
       <c r="C67" t="n">
         <v>35.61558151245117</v>
@@ -1974,7 +1974,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>16.90422439575195</v>
+        <v>16.90422821044922</v>
       </c>
       <c r="C70" t="n">
         <v>28.18866539001465</v>
@@ -2032,7 +2032,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>19.49991798400879</v>
+        <v>19.49992179870605</v>
       </c>
       <c r="C72" t="n">
         <v>32.51711273193359</v>
@@ -2061,7 +2061,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>18.96977615356445</v>
+        <v>18.96977043151855</v>
       </c>
       <c r="C73" t="n">
         <v>31.6164722442627</v>
@@ -2090,7 +2090,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>21.17564964294434</v>
+        <v>21.17565727233887</v>
       </c>
       <c r="C74" t="n">
         <v>35.29296112060547</v>
@@ -2119,7 +2119,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>21.30470085144043</v>
+        <v>21.3046989440918</v>
       </c>
       <c r="C75" t="n">
         <v>35.50804138183594</v>
@@ -2148,7 +2148,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>22.5932731628418</v>
+        <v>22.59327507019043</v>
       </c>
       <c r="C76" t="n">
         <v>37.63865661621094</v>
@@ -2177,7 +2177,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>21.87513542175293</v>
+        <v>21.87514114379883</v>
       </c>
       <c r="C77" t="n">
         <v>36.44228744506836</v>
@@ -2206,7 +2206,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>20.96737480163574</v>
+        <v>20.96736907958984</v>
       </c>
       <c r="C78" t="n">
         <v>34.93001937866211</v>
@@ -2235,7 +2235,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>21.02219390869141</v>
+        <v>21.02220153808594</v>
       </c>
       <c r="C79" t="n">
         <v>35.00395202636719</v>
@@ -2264,7 +2264,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>21.31686019897461</v>
+        <v>21.31686210632324</v>
       </c>
       <c r="C80" t="n">
         <v>35.49459838867188</v>
@@ -2293,7 +2293,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>21.62364387512207</v>
+        <v>21.62363433837891</v>
       </c>
       <c r="C81" t="n">
         <v>36.00540924072266</v>
@@ -2322,7 +2322,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>22.27160453796387</v>
+        <v>22.2716121673584</v>
       </c>
       <c r="C82" t="n">
         <v>37.06735610961914</v>
@@ -2351,7 +2351,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>20.89049339294434</v>
+        <v>20.89048767089844</v>
       </c>
       <c r="C83" t="n">
         <v>34.76871109008789</v>
@@ -2380,7 +2380,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>21.79508018493652</v>
+        <v>21.79507446289062</v>
       </c>
       <c r="C84" t="n">
         <v>36.27425765991211</v>
@@ -2409,7 +2409,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>22.58503341674805</v>
+        <v>22.58503150939941</v>
       </c>
       <c r="C85" t="n">
         <v>37.57144546508789</v>
@@ -2438,7 +2438,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>24.2132511138916</v>
+        <v>24.21325492858887</v>
       </c>
       <c r="C86" t="n">
         <v>40.28008651733398</v>
@@ -2467,7 +2467,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>24.88797187805176</v>
+        <v>24.88797950744629</v>
       </c>
       <c r="C87" t="n">
         <v>41.40252304077148</v>
@@ -2496,7 +2496,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>25.1204776763916</v>
+        <v>25.1204833984375</v>
       </c>
       <c r="C88" t="n">
         <v>41.77219009399414</v>
@@ -2525,7 +2525,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>24.63140487670898</v>
+        <v>24.63141441345215</v>
       </c>
       <c r="C89" t="n">
         <v>40.95892333984375</v>
@@ -2554,7 +2554,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>24.98709297180176</v>
+        <v>24.98710441589355</v>
       </c>
       <c r="C90" t="n">
         <v>41.55038833618164</v>
@@ -2583,7 +2583,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>25.59557151794434</v>
+        <v>25.59557342529297</v>
       </c>
       <c r="C91" t="n">
         <v>42.54512786865234</v>
@@ -2612,7 +2612,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>27.22916412353516</v>
+        <v>27.22916030883789</v>
       </c>
       <c r="C92" t="n">
         <v>45.2604866027832</v>
@@ -2641,7 +2641,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>26.49324035644531</v>
+        <v>26.49323463439941</v>
       </c>
       <c r="C93" t="n">
         <v>44.0372314453125</v>
@@ -2670,7 +2670,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>28.03994941711426</v>
+        <v>28.03995704650879</v>
       </c>
       <c r="C94" t="n">
         <v>46.59128189086914</v>
@@ -2699,7 +2699,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>29.16041946411133</v>
+        <v>29.16042137145996</v>
       </c>
       <c r="C95" t="n">
         <v>48.45305252075195</v>
@@ -2728,7 +2728,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>30.25660705566406</v>
+        <v>30.2566089630127</v>
       </c>
       <c r="C96" t="n">
         <v>50.27449417114258</v>
@@ -2757,7 +2757,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>31.23758697509766</v>
+        <v>31.23757934570312</v>
       </c>
       <c r="C97" t="n">
         <v>51.88758087158203</v>
@@ -2786,7 +2786,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>30.10056495666504</v>
+        <v>30.10056114196777</v>
       </c>
       <c r="C98" t="n">
         <v>49.99892425537109</v>
@@ -2815,7 +2815,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>30.95029258728027</v>
+        <v>30.95028877258301</v>
       </c>
       <c r="C99" t="n">
         <v>51.41037368774414</v>
@@ -2902,7 +2902,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>31.77796936035156</v>
+        <v>31.7779655456543</v>
       </c>
       <c r="C102" t="n">
         <v>52.71428680419922</v>
@@ -2931,7 +2931,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>31.9398193359375</v>
+        <v>31.9398365020752</v>
       </c>
       <c r="C103" t="n">
         <v>52.91592025756836</v>
@@ -2960,7 +2960,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>29.97224044799805</v>
+        <v>29.97223472595215</v>
       </c>
       <c r="C104" t="n">
         <v>49.65614318847656</v>
@@ -2989,7 +2989,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>31.07977485656738</v>
+        <v>31.07976722717285</v>
       </c>
       <c r="C105" t="n">
         <v>51.49102783203125</v>
@@ -3018,7 +3018,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>30.86404228210449</v>
+        <v>30.86405563354492</v>
       </c>
       <c r="C106" t="n">
         <v>51.06759262084961</v>
@@ -3047,7 +3047,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>32.65950393676758</v>
+        <v>32.65951919555664</v>
       </c>
       <c r="C107" t="n">
         <v>54.03836059570312</v>
@@ -3076,7 +3076,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>33.94314956665039</v>
+        <v>33.94314575195312</v>
       </c>
       <c r="C108" t="n">
         <v>56.16225433349609</v>
@@ -3105,7 +3105,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>34.85655212402344</v>
+        <v>34.85654067993164</v>
       </c>
       <c r="C109" t="n">
         <v>57.6073112487793</v>
@@ -3134,7 +3134,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>33.5023078918457</v>
+        <v>33.50228500366211</v>
       </c>
       <c r="C110" t="n">
         <v>55.36915588378906</v>
@@ -3163,7 +3163,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>35.49502944946289</v>
+        <v>35.49502563476562</v>
       </c>
       <c r="C111" t="n">
         <v>58.66253662109375</v>
@@ -3221,7 +3221,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>33.35135650634766</v>
+        <v>33.35136795043945</v>
       </c>
       <c r="C113" t="n">
         <v>55.03309631347656</v>
@@ -3250,7 +3250,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>35.15984725952148</v>
+        <v>35.15985488891602</v>
       </c>
       <c r="C114" t="n">
         <v>58.01730346679688</v>
@@ -3279,7 +3279,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>34.91749572753906</v>
+        <v>34.9174919128418</v>
       </c>
       <c r="C115" t="n">
         <v>57.52665710449219</v>
@@ -3308,7 +3308,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>37.35303497314453</v>
+        <v>37.3530387878418</v>
       </c>
       <c r="C116" t="n">
         <v>61.53920745849609</v>
@@ -3337,7 +3337,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>35.50087738037109</v>
+        <v>35.50088882446289</v>
       </c>
       <c r="C117" t="n">
         <v>58.48778533935547</v>
@@ -3366,7 +3366,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>34.81896209716797</v>
+        <v>34.81896591186523</v>
       </c>
       <c r="C118" t="n">
         <v>57.2712516784668</v>
@@ -3395,7 +3395,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>38.12882232666016</v>
+        <v>38.12882995605469</v>
       </c>
       <c r="C119" t="n">
         <v>62.71541213989258</v>
@@ -3424,7 +3424,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>39.38739395141602</v>
+        <v>39.38740539550781</v>
       </c>
       <c r="C120" t="n">
         <v>64.78553771972656</v>
@@ -3453,7 +3453,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>38.00762176513672</v>
+        <v>38.00762939453125</v>
       </c>
       <c r="C121" t="n">
         <v>62.4264030456543</v>
@@ -3511,7 +3511,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>36.53036499023438</v>
+        <v>36.53037643432617</v>
       </c>
       <c r="C123" t="n">
         <v>60.00005340576172</v>
@@ -3540,7 +3540,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>38.88346099853516</v>
+        <v>38.88345336914062</v>
       </c>
       <c r="C124" t="n">
         <v>63.75719833374023</v>
@@ -3598,7 +3598,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>40.3181266784668</v>
+        <v>40.31811141967773</v>
       </c>
       <c r="C126" t="n">
         <v>66.10961151123047</v>
@@ -3627,7 +3627,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>41.46771621704102</v>
+        <v>41.46773910522461</v>
       </c>
       <c r="C127" t="n">
         <v>67.88401031494141</v>
@@ -3656,7 +3656,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>68.60340118408203</v>
+        <v>68.60337066650391</v>
       </c>
       <c r="C128" t="n">
         <v>72.19858551025391</v>
@@ -3685,7 +3685,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>68.57811737060547</v>
+        <v>68.57813262939453</v>
       </c>
       <c r="C129" t="n">
         <v>72.17198944091797</v>
@@ -3714,7 +3714,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>66.14065551757812</v>
+        <v>66.14064025878906</v>
       </c>
       <c r="C130" t="n">
         <v>69.49468231201172</v>
@@ -3772,7 +3772,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>65.95501708984375</v>
+        <v>65.95503234863281</v>
       </c>
       <c r="C132" t="n">
         <v>69.29964447021484</v>
@@ -3801,7 +3801,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>65.78089904785156</v>
+        <v>65.78091430664062</v>
       </c>
       <c r="C133" t="n">
         <v>69.00709533691406</v>
@@ -3830,7 +3830,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>70.91899108886719</v>
+        <v>70.91896057128906</v>
       </c>
       <c r="C134" t="n">
         <v>74.39716339111328</v>
@@ -3859,7 +3859,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>72.29644012451172</v>
+        <v>72.29647827148438</v>
       </c>
       <c r="C135" t="n">
         <v>75.84220123291016</v>
@@ -3888,7 +3888,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>72.39756011962891</v>
+        <v>72.39753723144531</v>
       </c>
       <c r="C136" t="n">
         <v>75.82447052001953</v>
@@ -3917,7 +3917,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>70.53534698486328</v>
+        <v>70.53533935546875</v>
       </c>
       <c r="C137" t="n">
         <v>73.87411499023438</v>
@@ -3946,7 +3946,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>71.89813232421875</v>
+        <v>71.89816284179688</v>
       </c>
       <c r="C138" t="n">
         <v>75.30141448974609</v>
@@ -3975,7 +3975,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>71.55094909667969</v>
+        <v>71.55097198486328</v>
       </c>
       <c r="C139" t="n">
         <v>74.81382751464844</v>
@@ -4004,7 +4004,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>69.09219360351562</v>
+        <v>69.09217071533203</v>
       </c>
       <c r="C140" t="n">
         <v>72.24290466308594</v>
@@ -4033,7 +4033,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>70.72856140136719</v>
+        <v>70.72854614257812</v>
       </c>
       <c r="C141" t="n">
         <v>73.95390319824219</v>
@@ -4062,7 +4062,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>72.84885406494141</v>
+        <v>72.84883117675781</v>
       </c>
       <c r="C142" t="n">
         <v>76.04609680175781</v>
@@ -4091,7 +4091,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>78.36049652099609</v>
+        <v>78.36050415039062</v>
       </c>
       <c r="C143" t="n">
         <v>81.79964447021484</v>
@@ -4120,7 +4120,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>80.13541412353516</v>
+        <v>80.13542938232422</v>
       </c>
       <c r="C144" t="n">
         <v>83.65248107910156</v>
@@ -4149,7 +4149,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>78.94572448730469</v>
+        <v>78.94571685791016</v>
       </c>
       <c r="C145" t="n">
         <v>82.2872314453125</v>
@@ -4178,7 +4178,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>86.14115905761719</v>
+        <v>86.14115142822266</v>
       </c>
       <c r="C146" t="n">
         <v>89.7872314453125</v>
@@ -4207,7 +4207,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>83.16429901123047</v>
+        <v>83.16433715820312</v>
       </c>
       <c r="C147" t="n">
         <v>86.68439483642578</v>
@@ -4236,7 +4236,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>83.41211700439453</v>
+        <v>83.41212463378906</v>
       </c>
       <c r="C148" t="n">
         <v>86.79964447021484</v>
@@ -4265,7 +4265,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>85.46524810791016</v>
+        <v>85.46527099609375</v>
       </c>
       <c r="C149" t="n">
         <v>88.93617248535156</v>
@@ -4294,7 +4294,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>84.57926177978516</v>
+        <v>84.57926940917969</v>
       </c>
       <c r="C150" t="n">
         <v>88.01418304443359</v>
@@ -4323,7 +4323,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>84.20539855957031</v>
+        <v>84.20537567138672</v>
       </c>
       <c r="C151" t="n">
         <v>87.48226928710938</v>
@@ -4352,7 +4352,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>87.53329467773438</v>
+        <v>87.53330230712891</v>
       </c>
       <c r="C152" t="n">
         <v>90.93971252441406</v>
@@ -4381,7 +4381,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>88.35247802734375</v>
+        <v>88.35249328613281</v>
       </c>
       <c r="C153" t="n">
         <v>91.79077911376953</v>
@@ -4410,7 +4410,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>92.85791778564453</v>
+        <v>92.85791015625</v>
       </c>
       <c r="C154" t="n">
         <v>96.32978820800781</v>
@@ -4439,7 +4439,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>84.94457244873047</v>
+        <v>84.94456481933594</v>
       </c>
       <c r="C155" t="n">
         <v>88.12056732177734</v>
@@ -4468,7 +4468,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>93.60993957519531</v>
+        <v>93.60994720458984</v>
       </c>
       <c r="C156" t="n">
         <v>97.10993194580078</v>
@@ -4526,7 +4526,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>94.94120788574219</v>
+        <v>94.94122314453125</v>
       </c>
       <c r="C158" t="n">
         <v>98.33333587646484</v>
@@ -4555,7 +4555,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>108.721923828125</v>
+        <v>108.7219161987305</v>
       </c>
       <c r="C159" t="n">
         <v>112.6063842773438</v>
@@ -4584,7 +4584,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>113.1498947143555</v>
+        <v>113.1498641967773</v>
       </c>
       <c r="C160" t="n">
         <v>117.0390090942383</v>
@@ -4613,7 +4613,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>113.5098342895508</v>
+        <v>113.5098648071289</v>
       </c>
       <c r="C161" t="n">
         <v>117.4113464355469</v>
@@ -4671,7 +4671,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>122.6398468017578</v>
+        <v>122.6398773193359</v>
       </c>
       <c r="C163" t="n">
         <v>126.7021255493164</v>
@@ -4729,7 +4729,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>121.9276428222656</v>
+        <v>121.9276275634766</v>
       </c>
       <c r="C165" t="n">
         <v>125.96630859375</v>
@@ -4758,7 +4758,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>124.0821228027344</v>
+        <v>124.0821380615234</v>
       </c>
       <c r="C166" t="n">
         <v>128.0407867431641</v>
@@ -4787,7 +4787,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>118.4033660888672</v>
+        <v>118.4033737182617</v>
       </c>
       <c r="C167" t="n">
         <v>122.1808547973633</v>
@@ -4845,7 +4845,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>132.0034637451172</v>
+        <v>132.0034484863281</v>
       </c>
       <c r="C169" t="n">
         <v>136.0638275146484</v>
@@ -4874,7 +4874,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>138.3593902587891</v>
+        <v>138.3593597412109</v>
       </c>
       <c r="C170" t="n">
         <v>142.6152496337891</v>
@@ -4903,7 +4903,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>124.3488464355469</v>
+        <v>124.3488388061523</v>
       </c>
       <c r="C171" t="n">
         <v>128.1737518310547</v>
@@ -4932,7 +4932,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>119.2081298828125</v>
+        <v>119.2081527709961</v>
       </c>
       <c r="C172" t="n">
         <v>122.7039031982422</v>
@@ -4961,7 +4961,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>140.782958984375</v>
+        <v>140.7829284667969</v>
       </c>
       <c r="C173" t="n">
         <v>144.9113464355469</v>
@@ -4990,7 +4990,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>143.4959411621094</v>
+        <v>143.4959106445312</v>
       </c>
       <c r="C174" t="n">
         <v>147.7039031982422</v>
@@ -5019,7 +5019,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>152.4580993652344</v>
+        <v>152.4581298828125</v>
       </c>
       <c r="C175" t="n">
         <v>156.7641906738281</v>
@@ -5048,7 +5048,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>175.7109527587891</v>
+        <v>175.7109069824219</v>
       </c>
       <c r="C176" t="n">
         <v>180.6737518310547</v>
@@ -5077,7 +5077,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>178.0129089355469</v>
+        <v>178.012939453125</v>
       </c>
       <c r="C177" t="n">
         <v>183.0407867431641</v>
@@ -5135,7 +5135,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>198.0783081054688</v>
+        <v>198.0783233642578</v>
       </c>
       <c r="C179" t="n">
         <v>203.4929046630859</v>
@@ -5164,7 +5164,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>193.84130859375</v>
+        <v>193.8413238525391</v>
       </c>
       <c r="C180" t="n">
         <v>199.1400756835938</v>
@@ -5222,7 +5222,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>205.4082946777344</v>
+        <v>205.4083404541016</v>
       </c>
       <c r="C182" t="n">
         <v>210.8510589599609</v>
@@ -5251,7 +5251,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>189.7160491943359</v>
+        <v>189.7159881591797</v>
       </c>
       <c r="C183" t="n">
         <v>194.7429046630859</v>
@@ -5280,7 +5280,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>194.574462890625</v>
+        <v>194.5744323730469</v>
       </c>
       <c r="C184" t="n">
         <v>199.5390014648438</v>
@@ -5309,7 +5309,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>219.5229797363281</v>
+        <v>219.5230102539062</v>
       </c>
       <c r="C185" t="n">
         <v>225.1241149902344</v>
@@ -5338,7 +5338,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>221.4248352050781</v>
+        <v>221.4248199462891</v>
       </c>
       <c r="C186" t="n">
         <v>227.074462890625</v>
@@ -5367,7 +5367,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>232.1701049804688</v>
+        <v>232.1701354980469</v>
       </c>
       <c r="C187" t="n">
         <v>237.9078063964844</v>
@@ -5396,7 +5396,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>257.3717346191406</v>
+        <v>257.3717651367188</v>
       </c>
       <c r="C188" t="n">
         <v>263.7322692871094</v>
@@ -5425,7 +5425,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>280.4450988769531</v>
+        <v>280.4451599121094</v>
       </c>
       <c r="C189" t="n">
         <v>287.3758850097656</v>
@@ -5454,7 +5454,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>263.5665283203125</v>
+        <v>263.566650390625</v>
       </c>
       <c r="C190" t="n">
         <v>269.8936157226562</v>
@@ -5483,7 +5483,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>269.9124755859375</v>
+        <v>269.9125061035156</v>
       </c>
       <c r="C191" t="n">
         <v>276.391845703125</v>
@@ -5570,7 +5570,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>247.5812683105469</v>
+        <v>247.5812835693359</v>
       </c>
       <c r="C194" t="n">
         <v>253.3599243164062</v>
@@ -5599,7 +5599,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>237.7226715087891</v>
+        <v>237.7226867675781</v>
       </c>
       <c r="C195" t="n">
         <v>243.2712707519531</v>
@@ -5628,7 +5628,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>254.3354187011719</v>
+        <v>254.3355255126953</v>
       </c>
       <c r="C196" t="n">
         <v>260.0443115234375</v>
@@ -5657,7 +5657,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>217.7454223632812</v>
+        <v>217.7454528808594</v>
       </c>
       <c r="C197" t="n">
         <v>222.6329803466797</v>
@@ -5715,7 +5715,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>220.0413818359375</v>
+        <v>220.0414276123047</v>
       </c>
       <c r="C199" t="n">
         <v>224.7517700195312</v>
@@ -5744,7 +5744,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>252.9799346923828</v>
+        <v>252.9799652099609</v>
       </c>
       <c r="C200" t="n">
         <v>258.3953857421875</v>
@@ -5773,7 +5773,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>234.2670440673828</v>
+        <v>234.2670288085938</v>
       </c>
       <c r="C201" t="n">
         <v>239.2819213867188</v>
@@ -5802,7 +5802,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>224.3922271728516</v>
+        <v>224.3922576904297</v>
       </c>
       <c r="C202" t="n">
         <v>228.9804992675781</v>
@@ -5831,7 +5831,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>218.6410522460938</v>
+        <v>218.6410369873047</v>
       </c>
       <c r="C203" t="n">
         <v>223.1117095947266</v>
@@ -5889,7 +5889,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>230.8090057373047</v>
+        <v>230.8089752197266</v>
       </c>
       <c r="C205" t="n">
         <v>235.3014221191406</v>
@@ -5918,7 +5918,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>229.9046478271484</v>
+        <v>229.9046173095703</v>
       </c>
       <c r="C206" t="n">
         <v>234.3794403076172</v>
@@ -5947,7 +5947,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>215.2518157958984</v>
+        <v>215.2518920898438</v>
       </c>
       <c r="C207" t="n">
         <v>219.4414825439453</v>
@@ -5976,7 +5976,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>219.4131317138672</v>
+        <v>219.4131164550781</v>
       </c>
       <c r="C208" t="n">
         <v>223.4397125244141</v>
@@ -6034,7 +6034,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>199.8954467773438</v>
+        <v>199.8954315185547</v>
       </c>
       <c r="C210" t="n">
         <v>203.5638275146484</v>
@@ -6092,7 +6092,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>222.2978668212891</v>
+        <v>222.2978515625</v>
       </c>
       <c r="C212" t="n">
         <v>226.1170196533203</v>
@@ -6150,7 +6150,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>216.2318420410156</v>
+        <v>216.2318572998047</v>
       </c>
       <c r="C214" t="n">
         <v>219.9468078613281</v>
@@ -6208,7 +6208,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>219.8095855712891</v>
+        <v>219.8096008300781</v>
       </c>
       <c r="C216" t="n">
         <v>223.3099975585938</v>
@@ -6266,7 +6266,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>236.3930511474609</v>
+        <v>236.3930358886719</v>
       </c>
       <c r="C218" t="n">
         <v>239.9100036621094</v>
@@ -6382,7 +6382,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>253.3107147216797</v>
+        <v>253.3106994628906</v>
       </c>
       <c r="C222" t="n">
         <v>256.7999877929688</v>
@@ -6411,7 +6411,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>246.7197723388672</v>
+        <v>246.7197570800781</v>
       </c>
       <c r="C223" t="n">
         <v>249.8500061035156</v>
@@ -6469,7 +6469,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>265.9360046386719</v>
+        <v>265.9359436035156</v>
       </c>
       <c r="C225" t="n">
         <v>269.3099975585938</v>
@@ -6498,7 +6498,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>274.8047485351562</v>
+        <v>274.8047180175781</v>
       </c>
       <c r="C226" t="n">
         <v>278.0199890136719</v>
@@ -6527,7 +6527,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>242.8189849853516</v>
+        <v>242.8190002441406</v>
       </c>
       <c r="C227" t="n">
         <v>245.6600036621094</v>
@@ -6585,7 +6585,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>227.1604919433594</v>
+        <v>227.1604614257812</v>
       </c>
       <c r="C229" t="n">
         <v>229.5500030517578</v>
@@ -6614,7 +6614,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>220.4214019775391</v>
+        <v>220.42138671875</v>
       </c>
       <c r="C230" t="n">
         <v>222.7400054931641</v>
@@ -6643,7 +6643,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>205.5973052978516</v>
+        <v>205.5973205566406</v>
       </c>
       <c r="C231" t="n">
         <v>207.7599945068359</v>
@@ -6701,7 +6701,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>197.5559539794922</v>
+        <v>197.5559234619141</v>
       </c>
       <c r="C233" t="n">
         <v>199.3300018310547</v>
@@ -6730,7 +6730,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>188.2098541259766</v>
+        <v>188.2098693847656</v>
       </c>
       <c r="C234" t="n">
         <v>189.8999938964844</v>
@@ -6875,7 +6875,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>214.180419921875</v>
+        <v>214.1804046630859</v>
       </c>
       <c r="C239" t="n">
         <v>215.3800048828125</v>
@@ -6904,7 +6904,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>225.5168914794922</v>
+        <v>225.5169067382812</v>
       </c>
       <c r="C240" t="n">
         <v>226.7799987792969</v>
